--- a/excel_cases/CPU利用率超限步骤表.xlsx
+++ b/excel_cases/CPU利用率超限步骤表.xlsx
@@ -822,8 +822,8 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>display aaa offline-record statistics
-display aaa online-fail-record statistics</t>
+          <t>1. display aaa offline-record statistics
+2. display aaa online-fail-record statistics</t>
         </is>
       </c>
     </row>
